--- a/재정학/03_Exams/오후반 시험 결과 및 성적/재정학 오후반.xlsx
+++ b/재정학/03_Exams/오후반 시험 결과 및 성적/재정학 오후반.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Teaching\재정학\03_Exams\오후반 시험 결과 및 성적\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380A64C5-CF88-4C02-8B9A-DEDFA256BE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7485E8C8-9677-4F2D-A0F2-5FD616444F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1030,7 +1030,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10925174" y="3054350"/>
+              <a:off x="10925174" y="3213100"/>
               <a:ext cx="7083425" cy="3365500"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3231,7 +3231,7 @@
         <v>13</v>
       </c>
       <c r="F28">
-        <v>40.5</v>
+        <v>74</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="G43">
         <f>AVERAGE(F5:F41)</f>
-        <v>40.824324324324323</v>
+        <v>41.729729729729726</v>
       </c>
     </row>
     <row r="44" spans="2:12" ht="17" x14ac:dyDescent="0.45">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="G44">
         <f>STDEV(F5:F41)</f>
-        <v>17.310568470757417</v>
+        <v>18.148918928086552</v>
       </c>
     </row>
   </sheetData>
